--- a/materials/新版睡眠数据_修改版.xlsx
+++ b/materials/新版睡眠数据_修改版.xlsx
@@ -513,25 +513,25 @@
         <v>304.8</v>
       </c>
       <c r="C2" t="n">
-        <v>323.1</v>
+        <v>314.3</v>
       </c>
       <c r="D2" t="n">
         <v>0.612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.641</v>
+        <v>0.623</v>
       </c>
       <c r="F2" t="n">
         <v>153.3</v>
       </c>
       <c r="G2" t="n">
-        <v>112.9</v>
+        <v>121.7</v>
       </c>
       <c r="H2" t="n">
         <v>40.2</v>
       </c>
       <c r="I2" t="n">
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>26.4</v>
+        <v>20.6</v>
       </c>
       <c r="N2" t="n">
-        <v>15.7</v>
+        <v>18.4</v>
       </c>
       <c r="O2" t="n">
-        <v>13.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -562,25 +562,25 @@
         <v>249.2</v>
       </c>
       <c r="C3" t="n">
-        <v>258.5</v>
+        <v>271.9</v>
       </c>
       <c r="D3" t="n">
         <v>0.587</v>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.602</v>
       </c>
       <c r="F3" t="n">
         <v>135.7</v>
       </c>
       <c r="G3" t="n">
-        <v>99.8</v>
+        <v>113.5</v>
       </c>
       <c r="H3" t="n">
         <v>40</v>
       </c>
       <c r="I3" t="n">
-        <v>30.6</v>
+        <v>31.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>9.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>26.5</v>
+        <v>16.4</v>
       </c>
       <c r="N3" t="n">
-        <v>23.5</v>
+        <v>20.3</v>
       </c>
       <c r="O3" t="n">
-        <v>14.5</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="4">
@@ -611,25 +611,25 @@
         <v>439.5</v>
       </c>
       <c r="C4" t="n">
-        <v>447.5</v>
+        <v>443.6</v>
       </c>
       <c r="D4" t="n">
         <v>0.828</v>
       </c>
       <c r="E4" t="n">
-        <v>0.852</v>
+        <v>0.847</v>
       </c>
       <c r="F4" t="n">
         <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>54</v>
+        <v>58.7</v>
       </c>
       <c r="H4" t="n">
         <v>24.4</v>
       </c>
       <c r="I4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>19.4</v>
+        <v>12.4</v>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>25.8</v>
       </c>
       <c r="O4" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="5">
@@ -660,25 +660,25 @@
         <v>256.9</v>
       </c>
       <c r="C5" t="n">
-        <v>272</v>
+        <v>269.7</v>
       </c>
       <c r="D5" t="n">
         <v>0.591</v>
       </c>
       <c r="E5" t="n">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
       <c r="F5" t="n">
         <v>155</v>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>129.7</v>
       </c>
       <c r="H5" t="n">
         <v>22.5</v>
       </c>
       <c r="I5" t="n">
-        <v>16.8</v>
+        <v>17.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -686,19 +686,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>19.4</v>
+        <v>16.3</v>
       </c>
       <c r="N5" t="n">
-        <v>25.3</v>
+        <v>20.9</v>
       </c>
       <c r="O5" t="n">
-        <v>14.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="6">
@@ -709,25 +709,25 @@
         <v>250.6</v>
       </c>
       <c r="C6" t="n">
-        <v>269.4</v>
+        <v>266</v>
       </c>
       <c r="D6" t="n">
         <v>0.512</v>
       </c>
       <c r="E6" t="n">
-        <v>0.54</v>
+        <v>0.531</v>
       </c>
       <c r="F6" t="n">
         <v>197.2</v>
       </c>
       <c r="G6" t="n">
-        <v>163.1</v>
+        <v>158.6</v>
       </c>
       <c r="H6" t="n">
         <v>41.9</v>
       </c>
       <c r="I6" t="n">
-        <v>31.8</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -735,19 +735,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="L6" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="M6" t="n">
-        <v>17.3</v>
+        <v>19.6</v>
       </c>
       <c r="N6" t="n">
-        <v>24.1</v>
+        <v>11.2</v>
       </c>
       <c r="O6" t="n">
-        <v>13.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="7">
@@ -758,25 +758,25 @@
         <v>275.7</v>
       </c>
       <c r="C7" t="n">
-        <v>288</v>
+        <v>286.7</v>
       </c>
       <c r="D7" t="n">
         <v>0.653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.665</v>
+        <v>0.702</v>
       </c>
       <c r="F7" t="n">
         <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>104.4</v>
+        <v>95.2</v>
       </c>
       <c r="H7" t="n">
         <v>26.4</v>
       </c>
       <c r="I7" t="n">
-        <v>21.8</v>
+        <v>20.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>20.7</v>
       </c>
       <c r="N7" t="n">
-        <v>17.4</v>
+        <v>23.9</v>
       </c>
       <c r="O7" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -807,25 +807,25 @@
         <v>257.7</v>
       </c>
       <c r="C8" t="n">
-        <v>282.3</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
         <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>0.596</v>
+        <v>0.586</v>
       </c>
       <c r="F8" t="n">
         <v>162.2</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>121.9</v>
       </c>
       <c r="H8" t="n">
         <v>32.1</v>
       </c>
       <c r="I8" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="L8" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>15.5</v>
+        <v>24.8</v>
       </c>
       <c r="N8" t="n">
-        <v>28</v>
+        <v>29.6</v>
       </c>
       <c r="O8" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="9">
@@ -856,25 +856,25 @@
         <v>346.1</v>
       </c>
       <c r="C9" t="n">
-        <v>364.2</v>
+        <v>369.4</v>
       </c>
       <c r="D9" t="n">
         <v>0.734</v>
       </c>
       <c r="E9" t="n">
-        <v>0.774</v>
+        <v>0.746</v>
       </c>
       <c r="F9" t="n">
         <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>81.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>26.3</v>
       </c>
       <c r="I9" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="L9" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="N9" t="n">
-        <v>21.3</v>
+        <v>25.1</v>
       </c>
       <c r="O9" t="n">
-        <v>12.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="10">
@@ -905,25 +905,25 @@
         <v>278.9</v>
       </c>
       <c r="C10" t="n">
-        <v>330.4</v>
+        <v>319.4</v>
       </c>
       <c r="D10" t="n">
         <v>0.654</v>
       </c>
       <c r="E10" t="n">
-        <v>0.783</v>
+        <v>0.794</v>
       </c>
       <c r="F10" t="n">
         <v>103.1</v>
       </c>
       <c r="G10" t="n">
-        <v>49.5</v>
+        <v>43.3</v>
       </c>
       <c r="H10" t="n">
         <v>44.3</v>
       </c>
       <c r="I10" t="n">
-        <v>18.9</v>
+        <v>19.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="L10" t="n">
-        <v>19.7</v>
+        <v>21.4</v>
       </c>
       <c r="M10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="N10" t="n">
-        <v>57.3</v>
+        <v>55.3</v>
       </c>
       <c r="O10" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="11">
@@ -954,25 +954,25 @@
         <v>329</v>
       </c>
       <c r="C11" t="n">
-        <v>383.7</v>
+        <v>369.1</v>
       </c>
       <c r="D11" t="n">
         <v>0.67</v>
       </c>
       <c r="E11" t="n">
-        <v>0.75</v>
+        <v>0.767</v>
       </c>
       <c r="F11" t="n">
         <v>137</v>
       </c>
       <c r="G11" t="n">
-        <v>74.5</v>
+        <v>63.3</v>
       </c>
       <c r="H11" t="n">
         <v>24.8</v>
       </c>
       <c r="I11" t="n">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>16.6</v>
+        <v>12.2</v>
       </c>
       <c r="L11" t="n">
-        <v>11.9</v>
+        <v>14.5</v>
       </c>
       <c r="M11" t="n">
-        <v>45.6</v>
+        <v>53.8</v>
       </c>
       <c r="N11" t="n">
-        <v>48.4</v>
+        <v>41.5</v>
       </c>
       <c r="O11" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="12">
@@ -1003,25 +1003,25 @@
         <v>257.5</v>
       </c>
       <c r="C12" t="n">
-        <v>308.8</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
         <v>0.549</v>
       </c>
       <c r="E12" t="n">
-        <v>0.648</v>
+        <v>0.639</v>
       </c>
       <c r="F12" t="n">
         <v>190.4</v>
       </c>
       <c r="G12" t="n">
-        <v>112.4</v>
+        <v>96.8</v>
       </c>
       <c r="H12" t="n">
         <v>21.1</v>
       </c>
       <c r="I12" t="n">
-        <v>8.5</v>
+        <v>11.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>19.9</v>
+        <v>24.7</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>16.4</v>
       </c>
       <c r="M12" t="n">
-        <v>41</v>
+        <v>49.2</v>
       </c>
       <c r="N12" t="n">
-        <v>59.7</v>
+        <v>44.1</v>
       </c>
       <c r="O12" t="n">
-        <v>34.7</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="13">
@@ -1052,25 +1052,25 @@
         <v>343.2</v>
       </c>
       <c r="C13" t="n">
-        <v>388.8</v>
+        <v>410.3</v>
       </c>
       <c r="D13" t="n">
         <v>0.671</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="F13" t="n">
         <v>132.4</v>
       </c>
       <c r="G13" t="n">
-        <v>66.5</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
         <v>35.6</v>
       </c>
       <c r="I13" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>13.3</v>
+        <v>19.6</v>
       </c>
       <c r="L13" t="n">
-        <v>20.7</v>
+        <v>16.8</v>
       </c>
       <c r="M13" t="n">
-        <v>49.8</v>
+        <v>53.2</v>
       </c>
       <c r="N13" t="n">
-        <v>40.7</v>
+        <v>39.9</v>
       </c>
       <c r="O13" t="n">
-        <v>31.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="14">
@@ -1101,25 +1101,25 @@
         <v>347</v>
       </c>
       <c r="C14" t="n">
-        <v>398.3</v>
+        <v>419.7</v>
       </c>
       <c r="D14" t="n">
         <v>0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>0.862</v>
+        <v>0.874</v>
       </c>
       <c r="F14" t="n">
         <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>38.4</v>
+        <v>35.6</v>
       </c>
       <c r="H14" t="n">
         <v>38.6</v>
       </c>
       <c r="I14" t="n">
-        <v>20.5</v>
+        <v>17.3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>14.8</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>45.9</v>
+        <v>49.9</v>
       </c>
       <c r="N14" t="n">
-        <v>46.9</v>
+        <v>55.2</v>
       </c>
       <c r="O14" t="n">
-        <v>30.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="15">
@@ -1150,45 +1150,45 @@
         <v>284.4</v>
       </c>
       <c r="C15" t="n">
-        <v>359.1</v>
+        <v>318.6</v>
       </c>
       <c r="D15" t="n">
         <v>0.635</v>
       </c>
       <c r="E15" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="F15" t="n">
         <v>141.8</v>
       </c>
       <c r="G15" t="n">
-        <v>73.8</v>
+        <v>69.8</v>
       </c>
       <c r="H15" t="n">
         <v>21.6</v>
       </c>
       <c r="I15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>26.3</v>
-      </c>
       <c r="L15" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="M15" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="N15" t="n">
-        <v>44.4</v>
+        <v>57.9</v>
       </c>
       <c r="O15" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="16">
@@ -1199,25 +1199,25 @@
         <v>251.9</v>
       </c>
       <c r="C16" t="n">
-        <v>329.1</v>
+        <v>290.4</v>
       </c>
       <c r="D16" t="n">
         <v>0.529</v>
       </c>
       <c r="E16" t="n">
-        <v>0.599</v>
+        <v>0.636</v>
       </c>
       <c r="F16" t="n">
         <v>182</v>
       </c>
       <c r="G16" t="n">
-        <v>96.5</v>
+        <v>80.8</v>
       </c>
       <c r="H16" t="n">
         <v>42.2</v>
       </c>
       <c r="I16" t="n">
-        <v>16.2</v>
+        <v>18.4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>30.6</v>
+        <v>15.3</v>
       </c>
       <c r="L16" t="n">
-        <v>13.2</v>
+        <v>20.2</v>
       </c>
       <c r="M16" t="n">
-        <v>47</v>
+        <v>55.6</v>
       </c>
       <c r="N16" t="n">
-        <v>61.6</v>
+        <v>56.4</v>
       </c>
       <c r="O16" t="n">
-        <v>38.1</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="17">
@@ -1248,25 +1248,25 @@
         <v>334.3</v>
       </c>
       <c r="C17" t="n">
-        <v>389.4</v>
+        <v>413.1</v>
       </c>
       <c r="D17" t="n">
         <v>0.64</v>
       </c>
       <c r="E17" t="n">
-        <v>0.766</v>
+        <v>0.708</v>
       </c>
       <c r="F17" t="n">
         <v>149.9</v>
       </c>
       <c r="G17" t="n">
-        <v>81.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>38.2</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>16.5</v>
+        <v>23.6</v>
       </c>
       <c r="L17" t="n">
-        <v>19.7</v>
+        <v>10.6</v>
       </c>
       <c r="M17" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="N17" t="n">
-        <v>47.6</v>
+        <v>42.4</v>
       </c>
       <c r="O17" t="n">
-        <v>32.4</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="18">
@@ -1297,25 +1297,25 @@
         <v>369.7</v>
       </c>
       <c r="C18" t="n">
-        <v>430.9</v>
+        <v>399.8</v>
       </c>
       <c r="D18" t="n">
         <v>0.746</v>
       </c>
       <c r="E18" t="n">
-        <v>0.854</v>
+        <v>0.886</v>
       </c>
       <c r="F18" t="n">
         <v>85.3</v>
       </c>
       <c r="G18" t="n">
-        <v>49.7</v>
+        <v>34.6</v>
       </c>
       <c r="H18" t="n">
         <v>40.5</v>
       </c>
       <c r="I18" t="n">
-        <v>20.8</v>
+        <v>23.7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>16.6</v>
+        <v>8.1</v>
       </c>
       <c r="L18" t="n">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="M18" t="n">
-        <v>41.7</v>
+        <v>59.4</v>
       </c>
       <c r="N18" t="n">
-        <v>48.6</v>
+        <v>41.5</v>
       </c>
       <c r="O18" t="n">
-        <v>30.4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -1346,25 +1346,25 @@
         <v>317.8</v>
       </c>
       <c r="C19" t="n">
-        <v>353.6</v>
+        <v>370.7</v>
       </c>
       <c r="D19" t="n">
         <v>0.747</v>
       </c>
       <c r="E19" t="n">
-        <v>0.851</v>
+        <v>0.858</v>
       </c>
       <c r="F19" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="H19" t="n">
         <v>20.1</v>
       </c>
       <c r="I19" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1372,19 +1372,19 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>11.3</v>
+        <v>16.6</v>
       </c>
       <c r="L19" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N19" t="n">
-        <v>58.2</v>
+        <v>59.7</v>
       </c>
       <c r="O19" t="n">
-        <v>35.8</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="20">
@@ -1395,25 +1395,25 @@
         <v>241</v>
       </c>
       <c r="C20" t="n">
-        <v>286.9</v>
+        <v>273.5</v>
       </c>
       <c r="D20" t="n">
         <v>0.523</v>
       </c>
       <c r="E20" t="n">
-        <v>0.61</v>
+        <v>0.602</v>
       </c>
       <c r="F20" t="n">
         <v>181.7</v>
       </c>
       <c r="G20" t="n">
-        <v>102.3</v>
+        <v>104.8</v>
       </c>
       <c r="H20" t="n">
         <v>38.4</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>20.1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="L20" t="n">
-        <v>16.6</v>
+        <v>15.1</v>
       </c>
       <c r="M20" t="n">
-        <v>43.7</v>
+        <v>42.3</v>
       </c>
       <c r="N20" t="n">
-        <v>58.3</v>
+        <v>47.7</v>
       </c>
       <c r="O20" t="n">
-        <v>34.4</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="21">
@@ -1444,25 +1444,25 @@
         <v>329.9</v>
       </c>
       <c r="C21" t="n">
-        <v>380.6</v>
+        <v>392.5</v>
       </c>
       <c r="D21" t="n">
         <v>0.702</v>
       </c>
       <c r="E21" t="n">
-        <v>0.786</v>
+        <v>0.835</v>
       </c>
       <c r="F21" t="n">
         <v>117.9</v>
       </c>
       <c r="G21" t="n">
-        <v>51.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H21" t="n">
         <v>22</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1470,19 +1470,19 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>15.4</v>
+        <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>12</v>
+        <v>18.9</v>
       </c>
       <c r="M21" t="n">
-        <v>56.1</v>
+        <v>43.9</v>
       </c>
       <c r="N21" t="n">
-        <v>45.5</v>
+        <v>38.6</v>
       </c>
       <c r="O21" t="n">
-        <v>32.2</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="22">
@@ -1493,25 +1493,25 @@
         <v>373.8</v>
       </c>
       <c r="C22" t="n">
-        <v>477.9</v>
+        <v>501.8</v>
       </c>
       <c r="D22" t="n">
         <v>0.801</v>
       </c>
       <c r="E22" t="n">
-        <v>0.96</v>
+        <v>0.944</v>
       </c>
       <c r="F22" t="n">
         <v>57.2</v>
       </c>
       <c r="G22" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="H22" t="n">
         <v>35.7</v>
       </c>
       <c r="I22" t="n">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>27.8</v>
+        <v>34.2</v>
       </c>
       <c r="L22" t="n">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
       <c r="M22" t="n">
-        <v>83.2</v>
+        <v>78.3</v>
       </c>
       <c r="N22" t="n">
-        <v>80.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="23">
@@ -1542,25 +1542,25 @@
         <v>296.1</v>
       </c>
       <c r="C23" t="n">
-        <v>422.6</v>
+        <v>384.6</v>
       </c>
       <c r="D23" t="n">
         <v>0.603</v>
       </c>
       <c r="E23" t="n">
-        <v>0.783</v>
+        <v>0.836</v>
       </c>
       <c r="F23" t="n">
         <v>151.6</v>
       </c>
       <c r="G23" t="n">
-        <v>32.1</v>
+        <v>40.5</v>
       </c>
       <c r="H23" t="n">
         <v>43.7</v>
       </c>
       <c r="I23" t="n">
-        <v>11.3</v>
+        <v>6.7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1568,19 +1568,19 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>42.7</v>
+        <v>29.9</v>
       </c>
       <c r="L23" t="n">
-        <v>29.9</v>
+        <v>38.6</v>
       </c>
       <c r="M23" t="n">
-        <v>78.8</v>
+        <v>73.3</v>
       </c>
       <c r="N23" t="n">
-        <v>74.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="O23" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="24">
@@ -1591,25 +1591,25 @@
         <v>245.4</v>
       </c>
       <c r="C24" t="n">
-        <v>363.7</v>
+        <v>366.4</v>
       </c>
       <c r="D24" t="n">
         <v>0.537</v>
       </c>
       <c r="E24" t="n">
-        <v>0.747</v>
+        <v>0.72</v>
       </c>
       <c r="F24" t="n">
         <v>176.2</v>
       </c>
       <c r="G24" t="n">
-        <v>32.3</v>
+        <v>54.7</v>
       </c>
       <c r="H24" t="n">
         <v>35.7</v>
       </c>
       <c r="I24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>48.2</v>
+        <v>49.3</v>
       </c>
       <c r="L24" t="n">
-        <v>39.1</v>
+        <v>34.1</v>
       </c>
       <c r="M24" t="n">
-        <v>81.7</v>
+        <v>69</v>
       </c>
       <c r="N24" t="n">
-        <v>70.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>60</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="25">
@@ -1640,25 +1640,25 @@
         <v>363.1</v>
       </c>
       <c r="C25" t="n">
-        <v>471.4</v>
+        <v>506.6</v>
       </c>
       <c r="D25" t="n">
         <v>0.707</v>
       </c>
       <c r="E25" t="n">
-        <v>0.947</v>
+        <v>0.879</v>
       </c>
       <c r="F25" t="n">
         <v>107</v>
       </c>
       <c r="G25" t="n">
-        <v>21.6</v>
+        <v>16.1</v>
       </c>
       <c r="H25" t="n">
         <v>43.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10.4</v>
+        <v>13</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>29.8</v>
+        <v>39.5</v>
       </c>
       <c r="L25" t="n">
-        <v>33.9</v>
+        <v>24.3</v>
       </c>
       <c r="M25" t="n">
-        <v>79.8</v>
+        <v>85</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O25" t="n">
-        <v>54.9</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="26">
@@ -1695,13 +1695,13 @@
         <v>0.759</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="F26" t="n">
         <v>71.2</v>
       </c>
       <c r="G26" t="n">
-        <v>16.5</v>
+        <v>15.1</v>
       </c>
       <c r="H26" t="n">
         <v>34.5</v>
@@ -1718,16 +1718,16 @@
         <v>42.2</v>
       </c>
       <c r="L26" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="M26" t="n">
-        <v>76.8</v>
+        <v>78.8</v>
       </c>
       <c r="N26" t="n">
         <v>70.7</v>
       </c>
       <c r="O26" t="n">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="27">
@@ -1738,25 +1738,25 @@
         <v>283.1</v>
       </c>
       <c r="C27" t="n">
-        <v>418.6</v>
+        <v>404.9</v>
       </c>
       <c r="D27" t="n">
         <v>0.585</v>
       </c>
       <c r="E27" t="n">
-        <v>0.801</v>
+        <v>0.789</v>
       </c>
       <c r="F27" t="n">
         <v>170.4</v>
       </c>
       <c r="G27" t="n">
-        <v>44.3</v>
+        <v>28.6</v>
       </c>
       <c r="H27" t="n">
         <v>30.2</v>
       </c>
       <c r="I27" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>47.9</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>36.9</v>
+        <v>34.9</v>
       </c>
       <c r="M27" t="n">
-        <v>74</v>
+        <v>83.2</v>
       </c>
       <c r="N27" t="n">
-        <v>79.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="O27" t="n">
-        <v>59.5</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="28">
@@ -1787,25 +1787,25 @@
         <v>297.7</v>
       </c>
       <c r="C28" t="n">
-        <v>404.1</v>
+        <v>436.1</v>
       </c>
       <c r="D28" t="n">
         <v>0.652</v>
       </c>
       <c r="E28" t="n">
-        <v>0.851</v>
+        <v>0.858</v>
       </c>
       <c r="F28" t="n">
         <v>125.7</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>38.7</v>
       </c>
       <c r="H28" t="n">
         <v>33.1</v>
       </c>
       <c r="I28" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1813,19 +1813,19 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>35.7</v>
+        <v>46.5</v>
       </c>
       <c r="L28" t="n">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="M28" t="n">
-        <v>84.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="N28" t="n">
-        <v>80.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="O28" t="n">
-        <v>57.7</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="29">
@@ -1836,25 +1836,25 @@
         <v>271.4</v>
       </c>
       <c r="C29" t="n">
-        <v>359</v>
+        <v>368.6</v>
       </c>
       <c r="D29" t="n">
         <v>0.599</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.799</v>
       </c>
       <c r="F29" t="n">
         <v>157.6</v>
       </c>
       <c r="G29" t="n">
-        <v>25.8</v>
+        <v>41.8</v>
       </c>
       <c r="H29" t="n">
         <v>24.1</v>
       </c>
       <c r="I29" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1862,19 +1862,19 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>32.3</v>
+        <v>35.8</v>
       </c>
       <c r="L29" t="n">
-        <v>34.9</v>
+        <v>33.4</v>
       </c>
       <c r="M29" t="n">
-        <v>83.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="N29" t="n">
-        <v>79.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>57.6</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="30">
@@ -1885,25 +1885,25 @@
         <v>280.4</v>
       </c>
       <c r="C30" t="n">
-        <v>444.8</v>
+        <v>421.3</v>
       </c>
       <c r="D30" t="n">
         <v>0.585</v>
       </c>
       <c r="E30" t="n">
-        <v>0.839</v>
+        <v>0.772</v>
       </c>
       <c r="F30" t="n">
         <v>165.5</v>
       </c>
       <c r="G30" t="n">
-        <v>11.7</v>
+        <v>43.9</v>
       </c>
       <c r="H30" t="n">
         <v>33.2</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1911,19 +1911,19 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>58.6</v>
+        <v>50.2</v>
       </c>
       <c r="L30" t="n">
-        <v>43.4</v>
+        <v>32</v>
       </c>
       <c r="M30" t="n">
-        <v>92.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="N30" t="n">
-        <v>96.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>72.8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -1934,25 +1934,25 @@
         <v>350.2</v>
       </c>
       <c r="C31" t="n">
-        <v>550.8</v>
+        <v>515.5</v>
       </c>
       <c r="D31" t="n">
         <v>0.828</v>
       </c>
       <c r="E31" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="F31" t="n">
         <v>38.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="H31" t="n">
         <v>34.7</v>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1960,68 +1960,68 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>57.3</v>
+        <v>47.2</v>
       </c>
       <c r="L31" t="n">
-        <v>15.9</v>
+        <v>11.1</v>
       </c>
       <c r="M31" t="n">
-        <v>93.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>90.2</v>
+        <v>94.8</v>
       </c>
       <c r="O31" t="n">
-        <v>64.2</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="n">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="C32" t="n">
-        <v>368.6</v>
+        <v>480.6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.709</v>
+        <v>0.7</v>
       </c>
       <c r="E32" t="n">
-        <v>0.727</v>
+        <v>0.914</v>
       </c>
       <c r="F32" t="n">
-        <v>102.2</v>
+        <v>148.4</v>
       </c>
       <c r="G32" t="n">
-        <v>76.90000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="H32" t="n">
-        <v>41.4</v>
+        <v>31</v>
       </c>
       <c r="I32" t="n">
-        <v>32.9</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>显效</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>60.7</v>
       </c>
       <c r="L32" t="n">
-        <v>2.5</v>
+        <v>30.6</v>
       </c>
       <c r="M32" t="n">
-        <v>24.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>20.5</v>
+        <v>94.2</v>
       </c>
       <c r="O32" t="n">
-        <v>13.3</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2029,48 +2029,48 @@
         <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>288.4</v>
+        <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>364</v>
+        <v>365.2</v>
       </c>
       <c r="D33" t="n">
-        <v>0.552</v>
+        <v>0.709</v>
       </c>
       <c r="E33" t="n">
-        <v>0.678</v>
+        <v>0.731</v>
       </c>
       <c r="F33" t="n">
-        <v>214</v>
+        <v>102.2</v>
       </c>
       <c r="G33" t="n">
-        <v>117.5</v>
+        <v>75.8</v>
       </c>
       <c r="H33" t="n">
-        <v>20.1</v>
+        <v>41.4</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>30.2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>26.2</v>
+        <v>4.3</v>
       </c>
       <c r="L33" t="n">
-        <v>22.8</v>
+        <v>3.1</v>
       </c>
       <c r="M33" t="n">
-        <v>45.1</v>
+        <v>25.8</v>
       </c>
       <c r="N33" t="n">
-        <v>60.2</v>
+        <v>27.1</v>
       </c>
       <c r="O33" t="n">
-        <v>38.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="34">
@@ -2078,28 +2078,28 @@
         <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>346.8</v>
+        <v>288.4</v>
       </c>
       <c r="C34" t="n">
-        <v>426.1</v>
+        <v>361</v>
       </c>
       <c r="D34" t="n">
-        <v>0.75</v>
+        <v>0.552</v>
       </c>
       <c r="E34" t="n">
-        <v>0.848</v>
+        <v>0.667</v>
       </c>
       <c r="F34" t="n">
-        <v>71.5</v>
+        <v>214</v>
       </c>
       <c r="G34" t="n">
-        <v>41.2</v>
+        <v>123.2</v>
       </c>
       <c r="H34" t="n">
-        <v>44</v>
+        <v>20.1</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2107,19 +2107,19 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>22.9</v>
+        <v>25.2</v>
       </c>
       <c r="L34" t="n">
-        <v>13.1</v>
+        <v>20.8</v>
       </c>
       <c r="M34" t="n">
         <v>42.4</v>
       </c>
       <c r="N34" t="n">
-        <v>54.5</v>
+        <v>47.8</v>
       </c>
       <c r="O34" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -2127,28 +2127,28 @@
         <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>449.9</v>
+        <v>346.8</v>
       </c>
       <c r="C35" t="n">
-        <v>496.5</v>
+        <v>390.2</v>
       </c>
       <c r="D35" t="n">
-        <v>0.835</v>
+        <v>0.75</v>
       </c>
       <c r="E35" t="n">
-        <v>0.946</v>
+        <v>0.865</v>
       </c>
       <c r="F35" t="n">
-        <v>45.3</v>
+        <v>71.5</v>
       </c>
       <c r="G35" t="n">
-        <v>16.7</v>
+        <v>27</v>
       </c>
       <c r="H35" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="I35" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="L35" t="n">
-        <v>13.3</v>
+        <v>15.3</v>
       </c>
       <c r="M35" t="n">
-        <v>63.1</v>
+        <v>62.2</v>
       </c>
       <c r="N35" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="O35" t="n">
-        <v>34.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="36">
@@ -2176,28 +2176,28 @@
         <v>2</v>
       </c>
       <c r="B36" t="n">
-        <v>326.5</v>
+        <v>449.9</v>
       </c>
       <c r="C36" t="n">
-        <v>386.9</v>
+        <v>511.9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.746</v>
+        <v>0.835</v>
       </c>
       <c r="E36" t="n">
-        <v>0.827</v>
+        <v>0.963</v>
       </c>
       <c r="F36" t="n">
-        <v>83.40000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="G36" t="n">
-        <v>37.4</v>
+        <v>23.4</v>
       </c>
       <c r="H36" t="n">
-        <v>27.8</v>
+        <v>43.8</v>
       </c>
       <c r="I36" t="n">
-        <v>10.3</v>
+        <v>24.7</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2205,19 +2205,19 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>18.5</v>
+        <v>13.8</v>
       </c>
       <c r="L36" t="n">
-        <v>10.9</v>
+        <v>15.3</v>
       </c>
       <c r="M36" t="n">
-        <v>55.2</v>
+        <v>48.3</v>
       </c>
       <c r="N36" t="n">
-        <v>62.9</v>
+        <v>43.6</v>
       </c>
       <c r="O36" t="n">
-        <v>36.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="37">
@@ -2225,48 +2225,48 @@
         <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>299.9</v>
+        <v>326.5</v>
       </c>
       <c r="C37" t="n">
-        <v>415.7</v>
+        <v>398.7</v>
       </c>
       <c r="D37" t="n">
-        <v>0.698</v>
+        <v>0.746</v>
       </c>
       <c r="E37" t="n">
-        <v>0.895</v>
+        <v>0.828</v>
       </c>
       <c r="F37" t="n">
-        <v>101.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>21.3</v>
+        <v>43.8</v>
       </c>
       <c r="H37" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="I37" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>显效</t>
+          <t>有效</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>38.6</v>
+        <v>22.1</v>
       </c>
       <c r="L37" t="n">
-        <v>28.2</v>
+        <v>11</v>
       </c>
       <c r="M37" t="n">
-        <v>79.09999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="N37" t="n">
-        <v>72.2</v>
+        <v>62.2</v>
       </c>
       <c r="O37" t="n">
-        <v>54.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="38">
@@ -2274,28 +2274,28 @@
         <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>275.5</v>
+        <v>299.9</v>
       </c>
       <c r="C38" t="n">
-        <v>435.4</v>
+        <v>407.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.646</v>
+        <v>0.698</v>
       </c>
       <c r="E38" t="n">
-        <v>0.843</v>
+        <v>0.964</v>
       </c>
       <c r="F38" t="n">
-        <v>128</v>
+        <v>101.8</v>
       </c>
       <c r="G38" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="H38" t="n">
-        <v>23.1</v>
+        <v>28.1</v>
       </c>
       <c r="I38" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2303,19 +2303,19 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>58</v>
+        <v>35.8</v>
       </c>
       <c r="L38" t="n">
-        <v>30.5</v>
+        <v>38.1</v>
       </c>
       <c r="M38" t="n">
-        <v>91.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>76.2</v>
+        <v>86.5</v>
       </c>
       <c r="O38" t="n">
-        <v>64.2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39">
@@ -2323,28 +2323,28 @@
         <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>415.7</v>
+        <v>275.5</v>
       </c>
       <c r="C39" t="n">
-        <v>550.5</v>
+        <v>379.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.775</v>
+        <v>0.646</v>
       </c>
       <c r="E39" t="n">
-        <v>0.918</v>
+        <v>0.806</v>
       </c>
       <c r="F39" t="n">
-        <v>82.90000000000001</v>
+        <v>128</v>
       </c>
       <c r="G39" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="H39" t="n">
-        <v>38</v>
+        <v>23.1</v>
       </c>
       <c r="I39" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2352,19 +2352,19 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>32.4</v>
+        <v>37.6</v>
       </c>
       <c r="L39" t="n">
-        <v>18.5</v>
+        <v>24.8</v>
       </c>
       <c r="M39" t="n">
-        <v>83.2</v>
+        <v>89</v>
       </c>
       <c r="N39" t="n">
-        <v>79.7</v>
+        <v>74</v>
       </c>
       <c r="O39" t="n">
-        <v>53.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="40">
@@ -2372,28 +2372,28 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>277.1</v>
+        <v>415.7</v>
       </c>
       <c r="C40" t="n">
-        <v>404.1</v>
+        <v>539.9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.599</v>
+        <v>0.775</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>165.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>37.9</v>
+        <v>7.1</v>
       </c>
       <c r="H40" t="n">
-        <v>20.1</v>
+        <v>38</v>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>45.8</v>
+        <v>29.9</v>
       </c>
       <c r="L40" t="n">
-        <v>35.7</v>
+        <v>21.2</v>
       </c>
       <c r="M40" t="n">
-        <v>77.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>88.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>61.7</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="41">
@@ -2421,28 +2421,28 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>294.9</v>
+        <v>277.1</v>
       </c>
       <c r="C41" t="n">
-        <v>442.6</v>
+        <v>439.9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.554</v>
+        <v>0.599</v>
       </c>
       <c r="E41" t="n">
-        <v>0.705</v>
+        <v>0.775</v>
       </c>
       <c r="F41" t="n">
-        <v>211.6</v>
+        <v>165.5</v>
       </c>
       <c r="G41" t="n">
-        <v>36.6</v>
+        <v>37.1</v>
       </c>
       <c r="H41" t="n">
-        <v>25.9</v>
+        <v>20.1</v>
       </c>
       <c r="I41" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>50.1</v>
+        <v>58.8</v>
       </c>
       <c r="L41" t="n">
-        <v>27.3</v>
+        <v>29.4</v>
       </c>
       <c r="M41" t="n">
-        <v>82.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>77.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>59.3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
@@ -2470,28 +2470,28 @@
         <v>2</v>
       </c>
       <c r="B42" t="n">
-        <v>380.8</v>
+        <v>294.9</v>
       </c>
       <c r="C42" t="n">
-        <v>527.7</v>
+        <v>440.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.73</v>
+        <v>0.554</v>
       </c>
       <c r="E42" t="n">
-        <v>0.946</v>
+        <v>0.708</v>
       </c>
       <c r="F42" t="n">
-        <v>95.8</v>
+        <v>211.6</v>
       </c>
       <c r="G42" t="n">
-        <v>10.8</v>
+        <v>45.4</v>
       </c>
       <c r="H42" t="n">
-        <v>44.8</v>
+        <v>25.9</v>
       </c>
       <c r="I42" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2499,19 +2499,19 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>38.6</v>
+        <v>49.5</v>
       </c>
       <c r="L42" t="n">
-        <v>29.6</v>
+        <v>27.8</v>
       </c>
       <c r="M42" t="n">
-        <v>88.7</v>
+        <v>78.5</v>
       </c>
       <c r="N42" t="n">
-        <v>78.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="O42" t="n">
-        <v>58.8</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="43">
@@ -2519,28 +2519,28 @@
         <v>2</v>
       </c>
       <c r="B43" t="n">
-        <v>383</v>
+        <v>380.8</v>
       </c>
       <c r="C43" t="n">
-        <v>481.4</v>
+        <v>498.6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.827</v>
+        <v>0.73</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.914</v>
       </c>
       <c r="F43" t="n">
-        <v>40.5</v>
+        <v>95.8</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="H43" t="n">
-        <v>39.5</v>
+        <v>44.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2548,19 +2548,19 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>25.7</v>
+        <v>30.9</v>
       </c>
       <c r="L43" t="n">
-        <v>12.9</v>
+        <v>25.2</v>
       </c>
       <c r="M43" t="n">
-        <v>80.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>89.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44">
@@ -2568,28 +2568,28 @@
         <v>2</v>
       </c>
       <c r="B44" t="n">
-        <v>293.3</v>
+        <v>383</v>
       </c>
       <c r="C44" t="n">
-        <v>437.9</v>
+        <v>538.2</v>
       </c>
       <c r="D44" t="n">
-        <v>0.669</v>
+        <v>0.827</v>
       </c>
       <c r="E44" t="n">
-        <v>0.853</v>
+        <v>0.922</v>
       </c>
       <c r="F44" t="n">
-        <v>124.6</v>
+        <v>40.5</v>
       </c>
       <c r="G44" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="H44" t="n">
-        <v>20.7</v>
+        <v>39.5</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2597,19 +2597,19 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>49.3</v>
+        <v>40.5</v>
       </c>
       <c r="L44" t="n">
-        <v>27.5</v>
+        <v>11.5</v>
       </c>
       <c r="M44" t="n">
-        <v>86</v>
+        <v>79.3</v>
       </c>
       <c r="N44" t="n">
-        <v>75.8</v>
+        <v>83.5</v>
       </c>
       <c r="O44" t="n">
-        <v>59.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="45">
@@ -2617,28 +2617,28 @@
         <v>2</v>
       </c>
       <c r="B45" t="n">
-        <v>362.7</v>
+        <v>293.3</v>
       </c>
       <c r="C45" t="n">
-        <v>516.4</v>
+        <v>398.5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.844</v>
+        <v>0.669</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="F45" t="n">
-        <v>38.6</v>
+        <v>124.6</v>
       </c>
       <c r="G45" t="n">
-        <v>7.2</v>
+        <v>27.3</v>
       </c>
       <c r="H45" t="n">
-        <v>28.5</v>
+        <v>20.7</v>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>42.4</v>
+        <v>35.9</v>
       </c>
       <c r="L45" t="n">
-        <v>10.8</v>
+        <v>22.9</v>
       </c>
       <c r="M45" t="n">
-        <v>81.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>80.7</v>
+        <v>76.8</v>
       </c>
       <c r="O45" t="n">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="46">
@@ -2666,28 +2666,28 @@
         <v>2</v>
       </c>
       <c r="B46" t="n">
-        <v>366.1</v>
+        <v>362.7</v>
       </c>
       <c r="C46" t="n">
-        <v>472.7</v>
+        <v>518.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.717</v>
+        <v>0.844</v>
       </c>
       <c r="E46" t="n">
-        <v>0.944</v>
+        <v>0.923</v>
       </c>
       <c r="F46" t="n">
-        <v>113.4</v>
+        <v>38.6</v>
       </c>
       <c r="G46" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="H46" t="n">
-        <v>31</v>
+        <v>28.5</v>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>29.1</v>
+        <v>43</v>
       </c>
       <c r="L46" t="n">
-        <v>31.7</v>
+        <v>9.4</v>
       </c>
       <c r="M46" t="n">
-        <v>91.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>82.3</v>
+        <v>80</v>
       </c>
       <c r="O46" t="n">
-        <v>58.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="47">
@@ -2715,28 +2715,28 @@
         <v>2</v>
       </c>
       <c r="B47" t="n">
-        <v>256.5</v>
+        <v>366.1</v>
       </c>
       <c r="C47" t="n">
-        <v>406.2</v>
+        <v>499.3</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.717</v>
       </c>
       <c r="E47" t="n">
-        <v>0.776</v>
+        <v>0.889</v>
       </c>
       <c r="F47" t="n">
-        <v>177.5</v>
+        <v>113.4</v>
       </c>
       <c r="G47" t="n">
-        <v>32.3</v>
+        <v>19.9</v>
       </c>
       <c r="H47" t="n">
-        <v>23.2</v>
+        <v>31</v>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2744,19 +2744,19 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>58.4</v>
+        <v>36.4</v>
       </c>
       <c r="L47" t="n">
-        <v>38.3</v>
+        <v>24</v>
       </c>
       <c r="M47" t="n">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
       <c r="N47" t="n">
-        <v>75.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="O47" t="n">
-        <v>63.6</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="48">
@@ -2764,28 +2764,28 @@
         <v>2</v>
       </c>
       <c r="B48" t="n">
-        <v>348.1</v>
+        <v>256.5</v>
       </c>
       <c r="C48" t="n">
-        <v>463.2</v>
+        <v>375.5</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>0.931</v>
+        <v>0.83</v>
       </c>
       <c r="F48" t="n">
-        <v>121.6</v>
+        <v>177.5</v>
       </c>
       <c r="G48" t="n">
-        <v>10.4</v>
+        <v>29.3</v>
       </c>
       <c r="H48" t="n">
-        <v>32.7</v>
+        <v>23.2</v>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2793,19 +2793,19 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>33.1</v>
+        <v>46.4</v>
       </c>
       <c r="L48" t="n">
-        <v>34.3</v>
+        <v>48</v>
       </c>
       <c r="M48" t="n">
-        <v>91.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="N48" t="n">
-        <v>82.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="O48" t="n">
-        <v>60.4</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="49">
@@ -2813,28 +2813,28 @@
         <v>2</v>
       </c>
       <c r="B49" t="n">
-        <v>265.4</v>
+        <v>348.1</v>
       </c>
       <c r="C49" t="n">
-        <v>381.9</v>
+        <v>491.1</v>
       </c>
       <c r="D49" t="n">
-        <v>0.556</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.706</v>
+        <v>0.918</v>
       </c>
       <c r="F49" t="n">
-        <v>173.7</v>
+        <v>121.6</v>
       </c>
       <c r="G49" t="n">
-        <v>34.6</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>38</v>
+        <v>32.7</v>
       </c>
       <c r="I49" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2842,19 +2842,19 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>43.9</v>
+        <v>41.1</v>
       </c>
       <c r="L49" t="n">
-        <v>27</v>
+        <v>32.5</v>
       </c>
       <c r="M49" t="n">
-        <v>80.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="N49" t="n">
-        <v>81.3</v>
+        <v>88.7</v>
       </c>
       <c r="O49" t="n">
-        <v>58.1</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="50">
@@ -2862,28 +2862,28 @@
         <v>2</v>
       </c>
       <c r="B50" t="n">
-        <v>393</v>
+        <v>265.4</v>
       </c>
       <c r="C50" t="n">
-        <v>534.6</v>
+        <v>428.8</v>
       </c>
       <c r="D50" t="n">
-        <v>0.737</v>
+        <v>0.556</v>
       </c>
       <c r="E50" t="n">
-        <v>0.917</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>108.7</v>
+        <v>173.7</v>
       </c>
       <c r="G50" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="H50" t="n">
-        <v>31.6</v>
+        <v>38</v>
       </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>36</v>
+        <v>61.6</v>
       </c>
       <c r="L50" t="n">
-        <v>24.4</v>
+        <v>45.1</v>
       </c>
       <c r="M50" t="n">
-        <v>84.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>57.9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51">
@@ -2911,28 +2911,28 @@
         <v>2</v>
       </c>
       <c r="B51" t="n">
-        <v>412.3</v>
+        <v>393</v>
       </c>
       <c r="C51" t="n">
-        <v>515.1</v>
+        <v>499.1</v>
       </c>
       <c r="D51" t="n">
-        <v>0.827</v>
+        <v>0.737</v>
       </c>
       <c r="E51" t="n">
-        <v>0.922</v>
+        <v>0.904</v>
       </c>
       <c r="F51" t="n">
-        <v>61.6</v>
+        <v>108.7</v>
       </c>
       <c r="G51" t="n">
-        <v>6.1</v>
+        <v>16.5</v>
       </c>
       <c r="H51" t="n">
-        <v>24.5</v>
+        <v>31.6</v>
       </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2940,19 +2940,19 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>24.9</v>
+        <v>27</v>
       </c>
       <c r="L51" t="n">
-        <v>11.5</v>
+        <v>22.7</v>
       </c>
       <c r="M51" t="n">
-        <v>90.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="N51" t="n">
-        <v>84.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="O51" t="n">
-        <v>52.6</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="52">
@@ -2960,28 +2960,28 @@
         <v>2</v>
       </c>
       <c r="B52" t="n">
-        <v>278.7</v>
+        <v>412.3</v>
       </c>
       <c r="C52" t="n">
-        <v>420.2</v>
+        <v>528.1</v>
       </c>
       <c r="D52" t="n">
-        <v>0.612</v>
+        <v>0.827</v>
       </c>
       <c r="E52" t="n">
-        <v>0.87</v>
+        <v>0.912</v>
       </c>
       <c r="F52" t="n">
-        <v>150.1</v>
+        <v>61.6</v>
       </c>
       <c r="G52" t="n">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="H52" t="n">
-        <v>26.3</v>
+        <v>24.5</v>
       </c>
       <c r="I52" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2989,19 +2989,19 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>50.8</v>
+        <v>28.1</v>
       </c>
       <c r="L52" t="n">
-        <v>42.2</v>
+        <v>10.3</v>
       </c>
       <c r="M52" t="n">
-        <v>83.3</v>
+        <v>85.2</v>
       </c>
       <c r="N52" t="n">
-        <v>74.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>62.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="53">
@@ -3009,28 +3009,28 @@
         <v>2</v>
       </c>
       <c r="B53" t="n">
-        <v>440.7</v>
+        <v>278.7</v>
       </c>
       <c r="C53" t="n">
-        <v>597.8</v>
+        <v>435.4</v>
       </c>
       <c r="D53" t="n">
-        <v>0.827</v>
+        <v>0.612</v>
       </c>
       <c r="E53" t="n">
-        <v>0.959</v>
+        <v>0.755</v>
       </c>
       <c r="F53" t="n">
-        <v>64.09999999999999</v>
+        <v>150.1</v>
       </c>
       <c r="G53" t="n">
-        <v>5.8</v>
+        <v>22.6</v>
       </c>
       <c r="H53" t="n">
-        <v>28.3</v>
+        <v>26.3</v>
       </c>
       <c r="I53" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3038,19 +3038,19 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>35.6</v>
+        <v>56.2</v>
       </c>
       <c r="L53" t="n">
-        <v>16</v>
+        <v>23.4</v>
       </c>
       <c r="M53" t="n">
-        <v>91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>86.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="O53" t="n">
-        <v>57.3</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="54">
@@ -3058,28 +3058,28 @@
         <v>2</v>
       </c>
       <c r="B54" t="n">
-        <v>429.4</v>
+        <v>440.7</v>
       </c>
       <c r="C54" t="n">
-        <v>573.1</v>
+        <v>596.8</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.926</v>
       </c>
       <c r="F54" t="n">
-        <v>66.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>12.2</v>
+        <v>5.9</v>
       </c>
       <c r="H54" t="n">
-        <v>30.1</v>
+        <v>28.3</v>
       </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3087,19 +3087,19 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>33.5</v>
+        <v>35.4</v>
       </c>
       <c r="L54" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="M54" t="n">
-        <v>81.5</v>
+        <v>90.8</v>
       </c>
       <c r="N54" t="n">
-        <v>82.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O54" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55">
@@ -3107,28 +3107,28 @@
         <v>2</v>
       </c>
       <c r="B55" t="n">
-        <v>403.9</v>
+        <v>429.4</v>
       </c>
       <c r="C55" t="n">
-        <v>638.1</v>
+        <v>572.8</v>
       </c>
       <c r="D55" t="n">
-        <v>0.773</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>0.948</v>
+        <v>0.959</v>
       </c>
       <c r="F55" t="n">
-        <v>73.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>44.5</v>
+        <v>30.1</v>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3136,19 +3136,19 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>58</v>
+        <v>33.4</v>
       </c>
       <c r="L55" t="n">
-        <v>22.6</v>
+        <v>17.4</v>
       </c>
       <c r="M55" t="n">
-        <v>95.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>92.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>67.3</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="56">
@@ -3156,28 +3156,28 @@
         <v>2</v>
       </c>
       <c r="B56" t="n">
-        <v>440.1</v>
+        <v>403.9</v>
       </c>
       <c r="C56" t="n">
-        <v>621.7</v>
+        <v>604.7</v>
       </c>
       <c r="D56" t="n">
-        <v>0.843</v>
+        <v>0.773</v>
       </c>
       <c r="E56" t="n">
-        <v>0.91</v>
+        <v>0.961</v>
       </c>
       <c r="F56" t="n">
-        <v>56.8</v>
+        <v>73.8</v>
       </c>
       <c r="G56" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>25.3</v>
+        <v>44.5</v>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3185,19 +3185,19 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>41.3</v>
+        <v>49.7</v>
       </c>
       <c r="L56" t="n">
-        <v>7.9</v>
+        <v>24.3</v>
       </c>
       <c r="M56" t="n">
-        <v>93.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="N56" t="n">
-        <v>90.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>58.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3205,28 +3205,28 @@
         <v>2</v>
       </c>
       <c r="B57" t="n">
-        <v>367.2</v>
+        <v>440.1</v>
       </c>
       <c r="C57" t="n">
-        <v>596.4</v>
+        <v>652.5</v>
       </c>
       <c r="D57" t="n">
-        <v>0.758</v>
+        <v>0.843</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F57" t="n">
-        <v>72.7</v>
+        <v>56.8</v>
       </c>
       <c r="G57" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="H57" t="n">
-        <v>44.3</v>
+        <v>25.3</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3234,19 +3234,19 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>62.4</v>
+        <v>48.3</v>
       </c>
       <c r="L57" t="n">
-        <v>23.9</v>
+        <v>10.3</v>
       </c>
       <c r="M57" t="n">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N57" t="n">
-        <v>97.7</v>
+        <v>91.7</v>
       </c>
       <c r="O57" t="n">
-        <v>69.3</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="58">
@@ -3254,28 +3254,28 @@
         <v>2</v>
       </c>
       <c r="B58" t="n">
-        <v>340.6</v>
+        <v>367.2</v>
       </c>
       <c r="C58" t="n">
-        <v>569.9</v>
+        <v>574.6</v>
       </c>
       <c r="D58" t="n">
-        <v>0.718</v>
+        <v>0.758</v>
       </c>
       <c r="E58" t="n">
-        <v>0.969</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>98.7</v>
+        <v>72.7</v>
       </c>
       <c r="G58" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="H58" t="n">
-        <v>35.2</v>
+        <v>44.3</v>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>67.3</v>
+        <v>56.5</v>
       </c>
       <c r="L58" t="n">
-        <v>35</v>
+        <v>23.5</v>
       </c>
       <c r="M58" t="n">
-        <v>96.8</v>
+        <v>92.7</v>
       </c>
       <c r="N58" t="n">
-        <v>95.7</v>
+        <v>93</v>
       </c>
       <c r="O58" t="n">
-        <v>73.7</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3303,28 +3303,28 @@
         <v>2</v>
       </c>
       <c r="B59" t="n">
-        <v>343.7</v>
+        <v>340.6</v>
       </c>
       <c r="C59" t="n">
-        <v>515.1</v>
+        <v>522.2</v>
       </c>
       <c r="D59" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.718</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="F59" t="n">
-        <v>132.6</v>
+        <v>98.7</v>
       </c>
       <c r="G59" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="H59" t="n">
-        <v>22.1</v>
+        <v>35.2</v>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3332,19 +3332,19 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>49.9</v>
+        <v>53.3</v>
       </c>
       <c r="L59" t="n">
-        <v>35.2</v>
+        <v>33.6</v>
       </c>
       <c r="M59" t="n">
-        <v>95.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>94.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -3352,28 +3352,28 @@
         <v>2</v>
       </c>
       <c r="B60" t="n">
-        <v>367.3</v>
+        <v>343.7</v>
       </c>
       <c r="C60" t="n">
-        <v>564.8</v>
+        <v>564.9</v>
       </c>
       <c r="D60" t="n">
-        <v>0.822</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>0.916</v>
+        <v>0.956</v>
       </c>
       <c r="F60" t="n">
-        <v>48.1</v>
+        <v>132.6</v>
       </c>
       <c r="G60" t="n">
         <v>3</v>
       </c>
       <c r="H60" t="n">
-        <v>31.5</v>
+        <v>22.1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3381,19 +3381,19 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>53.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>11.4</v>
+        <v>38.6</v>
       </c>
       <c r="M60" t="n">
-        <v>93.8</v>
+        <v>97.7</v>
       </c>
       <c r="N60" t="n">
-        <v>97.5</v>
+        <v>93.7</v>
       </c>
       <c r="O60" t="n">
-        <v>64.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -3401,28 +3401,28 @@
         <v>2</v>
       </c>
       <c r="B61" t="n">
-        <v>377.7</v>
+        <v>367.3</v>
       </c>
       <c r="C61" t="n">
-        <v>577.9</v>
+        <v>572.8</v>
       </c>
       <c r="D61" t="n">
-        <v>0.716</v>
+        <v>0.822</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>120.6</v>
+        <v>48.1</v>
       </c>
       <c r="G61" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="H61" t="n">
-        <v>28.9</v>
+        <v>31.5</v>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3430,19 +3430,19 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>53</v>
+        <v>55.9</v>
       </c>
       <c r="L61" t="n">
-        <v>31</v>
+        <v>13.6</v>
       </c>
       <c r="M61" t="n">
-        <v>95.5</v>
+        <v>96</v>
       </c>
       <c r="N61" t="n">
-        <v>90</v>
+        <v>96.8</v>
       </c>
       <c r="O61" t="n">
-        <v>67.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -3450,45 +3450,45 @@
         <v>2</v>
       </c>
       <c r="B62" t="n">
-        <v>325.1</v>
+        <v>377.7</v>
       </c>
       <c r="C62" t="n">
-        <v>512.1</v>
+        <v>584.4</v>
       </c>
       <c r="D62" t="n">
-        <v>0.764</v>
+        <v>0.716</v>
       </c>
       <c r="E62" t="n">
-        <v>0.968</v>
+        <v>0.959</v>
       </c>
       <c r="F62" t="n">
-        <v>56.5</v>
+        <v>120.6</v>
       </c>
       <c r="G62" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I62" t="n">
         <v>1.8</v>
       </c>
-      <c r="H62" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>显效</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>57.5</v>
+        <v>54.7</v>
       </c>
       <c r="L62" t="n">
-        <v>26.7</v>
+        <v>33.9</v>
       </c>
       <c r="M62" t="n">
-        <v>96.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N62" t="n">
-        <v>96.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="O62" t="n">
         <v>69.3</v>
@@ -3499,48 +3499,48 @@
         <v>2</v>
       </c>
       <c r="B63" t="n">
-        <v>268</v>
+        <v>325.1</v>
       </c>
       <c r="C63" t="n">
-        <v>436.3</v>
+        <v>513.9</v>
       </c>
       <c r="D63" t="n">
-        <v>0.521</v>
+        <v>0.764</v>
       </c>
       <c r="E63" t="n">
-        <v>0.827</v>
+        <v>0.946</v>
       </c>
       <c r="F63" t="n">
-        <v>222.6</v>
+        <v>56.5</v>
       </c>
       <c r="G63" t="n">
-        <v>17.4</v>
+        <v>2.5</v>
       </c>
       <c r="H63" t="n">
-        <v>23.9</v>
+        <v>43.8</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>痊愈</t>
+          <t>显效</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>62.8</v>
+        <v>58.1</v>
       </c>
       <c r="L63" t="n">
-        <v>58.7</v>
+        <v>23.8</v>
       </c>
       <c r="M63" t="n">
-        <v>92.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>95</v>
+        <v>96.3</v>
       </c>
       <c r="O63" t="n">
-        <v>77.2</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
   </sheetData>
